--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$174</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5947" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5981" uniqueCount="663">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:24:31+00:00</t>
+    <t>2026-08-28T07:40:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1031,8 +1031,22 @@
     <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this.resolve()}
+</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>Procedure.basedOn:tumorkonferenz</t>
+  </si>
+  <si>
+    <t>tumorkonferenz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-tumorkonferenz)
+</t>
   </si>
   <si>
     <t>Procedure.partOf</t>
@@ -2378,7 +2392,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL173"/>
+  <dimension ref="A1:AL174"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.1015625" customWidth="true" bestFit="true"/>
@@ -8360,7 +8374,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>321</v>
       </c>
@@ -8435,16 +8449,14 @@
         <v>75</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="AC56" s="2"/>
       <c r="AD56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>321</v>
@@ -8459,7 +8471,7 @@
         <v>97</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>75</v>
@@ -8470,21 +8482,23 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="D57" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>86</v>
@@ -8496,16 +8510,16 @@
         <v>86</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8555,7 +8569,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8567,7 +8581,7 @@
         <v>97</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>75</v>
@@ -8578,42 +8592,42 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>75</v>
+        <v>333</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>86</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>161</v>
+        <v>334</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>10</v>
+        <v>335</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8639,13 +8653,13 @@
         <v>75</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>217</v>
+        <v>75</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>337</v>
+        <v>75</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>338</v>
+        <v>75</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>75</v>
@@ -8663,19 +8677,19 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>75</v>
@@ -8684,44 +8698,44 @@
         <v>75</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>340</v>
+        <v>75</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>214</v>
+        <v>161</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>341</v>
+        <v>10</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8747,13 +8761,13 @@
         <v>75</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>151</v>
+        <v>217</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>75</v>
@@ -8771,10 +8785,10 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>85</v>
@@ -8792,16 +8806,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>75</v>
+        <v>344</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8811,7 +8825,7 @@
         <v>85</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>75</v>
@@ -8823,13 +8837,13 @@
         <v>214</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8858,10 +8872,10 @@
         <v>151</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>75</v>
@@ -8879,7 +8893,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8900,12 +8914,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8919,24 +8933,26 @@
         <v>85</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>101</v>
+        <v>351</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>75</v>
@@ -8961,13 +8977,13 @@
         <v>75</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>75</v>
+        <v>354</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>75</v>
+        <v>355</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>75</v>
@@ -8985,7 +9001,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>103</v>
+        <v>350</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8994,10 +9010,10 @@
         <v>85</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>75</v>
@@ -9008,21 +9024,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>75</v>
@@ -9034,17 +9050,15 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>75</v>
@@ -9081,31 +9095,31 @@
         <v>75</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>75</v>
@@ -9116,14 +9130,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9139,23 +9153,21 @@
         <v>75</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>226</v>
+        <v>107</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>227</v>
+        <v>108</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>75</v>
       </c>
@@ -9191,9 +9203,11 @@
         <v>75</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AC63" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="AD63" t="s" s="2">
         <v>75</v>
       </c>
@@ -9201,7 +9215,7 @@
         <v>112</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9213,7 +9227,7 @@
         <v>97</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>75</v>
@@ -9222,16 +9236,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>75</v>
       </c>
@@ -9240,10 +9252,10 @@
         <v>76</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>75</v>
@@ -9255,10 +9267,10 @@
         <v>139</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>358</v>
+        <v>226</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>359</v>
+        <v>227</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>228</v>
@@ -9274,7 +9286,7 @@
         <v>75</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>360</v>
+        <v>75</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>75</v>
@@ -9289,26 +9301,26 @@
         <v>75</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>361</v>
+        <v>75</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>230</v>
@@ -9332,14 +9344,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="D65" t="s" s="2">
         <v>75</v>
       </c>
@@ -9351,25 +9365,29 @@
         <v>85</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>101</v>
+        <v>362</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>75</v>
       </c>
@@ -9378,7 +9396,7 @@
         <v>75</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>75</v>
+        <v>364</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>75</v>
@@ -9393,13 +9411,11 @@
         <v>75</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>75</v>
+        <v>365</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>75</v>
@@ -9417,19 +9433,19 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>75</v>
@@ -9440,21 +9456,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>75</v>
@@ -9466,17 +9482,15 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>75</v>
@@ -9513,31 +9527,31 @@
         <v>75</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>75</v>
@@ -9546,48 +9560,46 @@
         <v>75</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>75</v>
       </c>
@@ -9623,31 +9635,31 @@
         <v>75</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>75</v>
@@ -9656,12 +9668,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9669,13 +9681,13 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>75</v>
@@ -9684,18 +9696,20 @@
         <v>86</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>75</v>
       </c>
@@ -9743,7 +9757,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9764,12 +9778,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9777,13 +9791,13 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>75</v>
@@ -9792,20 +9806,18 @@
         <v>86</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>75</v>
       </c>
@@ -9853,7 +9865,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9874,12 +9886,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9887,13 +9899,13 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>75</v>
@@ -9902,19 +9914,19 @@
         <v>86</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>75</v>
@@ -9963,7 +9975,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9986,10 +9998,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10012,19 +10024,19 @@
         <v>86</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>267</v>
+        <v>376</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
@@ -10073,7 +10085,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10096,10 +10108,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10122,19 +10134,19 @@
         <v>86</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>75</v>
@@ -10183,7 +10195,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10204,26 +10216,26 @@
         <v>75</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>379</v>
+        <v>75</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>75</v>
@@ -10232,19 +10244,19 @@
         <v>86</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>214</v>
+        <v>100</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>63</v>
+        <v>272</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>380</v>
+        <v>273</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>349</v>
+        <v>274</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>75</v>
@@ -10269,13 +10281,13 @@
         <v>75</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>382</v>
+        <v>75</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>383</v>
+        <v>75</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>75</v>
@@ -10293,7 +10305,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>378</v>
+        <v>276</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10305,7 +10317,7 @@
         <v>97</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>384</v>
+        <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>75</v>
@@ -10314,44 +10326,48 @@
         <v>75</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>75</v>
+        <v>383</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>75</v>
       </c>
@@ -10375,13 +10391,13 @@
         <v>75</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>75</v>
+        <v>386</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>75</v>
+        <v>387</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>75</v>
@@ -10399,7 +10415,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>103</v>
+        <v>382</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10408,10 +10424,10 @@
         <v>85</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>75</v>
+        <v>388</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>75</v>
@@ -10422,21 +10438,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>75</v>
@@ -10448,17 +10464,15 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>75</v>
@@ -10495,31 +10509,31 @@
         <v>75</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>75</v>
@@ -10530,46 +10544,44 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>226</v>
+        <v>107</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>227</v>
+        <v>108</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>75</v>
       </c>
@@ -10605,9 +10617,11 @@
         <v>75</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AC76" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="AD76" t="s" s="2">
         <v>75</v>
       </c>
@@ -10615,7 +10629,7 @@
         <v>112</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10627,7 +10641,7 @@
         <v>97</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>75</v>
@@ -10636,25 +10650,23 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>389</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>86</v>
@@ -10666,16 +10678,16 @@
         <v>86</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>390</v>
+        <v>139</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>391</v>
+        <v>226</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>392</v>
+        <v>227</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>393</v>
+        <v>228</v>
       </c>
       <c r="O77" t="s" s="2">
         <v>229</v>
@@ -10688,7 +10700,7 @@
         <v>75</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>394</v>
+        <v>75</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>75</v>
@@ -10703,26 +10715,26 @@
         <v>75</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y77" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z77" t="s" s="2">
-        <v>395</v>
+        <v>75</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="AC77" s="2"/>
       <c r="AD77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>230</v>
@@ -10746,14 +10758,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>75</v>
       </c>
@@ -10765,25 +10779,29 @@
         <v>85</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>100</v>
+        <v>394</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>101</v>
+        <v>395</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>75</v>
       </c>
@@ -10792,7 +10810,7 @@
         <v>75</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>75</v>
+        <v>398</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>75</v>
@@ -10807,13 +10825,11 @@
         <v>75</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>75</v>
+        <v>399</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>75</v>
@@ -10831,19 +10847,19 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>75</v>
@@ -10854,21 +10870,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>75</v>
@@ -10880,17 +10896,15 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>75</v>
@@ -10927,31 +10941,31 @@
         <v>75</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>75</v>
@@ -10960,16 +10974,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C80" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>105</v>
       </c>
@@ -10978,10 +10990,10 @@
         <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>75</v>
@@ -10990,13 +11002,13 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>402</v>
+        <v>106</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>403</v>
+        <v>107</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>404</v>
+        <v>108</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>109</v>
@@ -11037,16 +11049,16 @@
         <v>75</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>113</v>
@@ -11072,18 +11084,20 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C81" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="B81" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>85</v>
@@ -11095,29 +11109,27 @@
         <v>75</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>127</v>
+        <v>406</v>
       </c>
       <c r="L81" t="s" s="2">
         <v>407</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>238</v>
+        <v>408</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>408</v>
+        <v>75</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>75</v>
@@ -11159,19 +11171,19 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>75</v>
@@ -11208,24 +11220,26 @@
         <v>86</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L82" t="s" s="2">
         <v>411</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>412</v>
+        <v>238</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>75</v>
+        <v>412</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>75</v>
@@ -11267,7 +11281,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -11285,15 +11299,15 @@
         <v>75</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>413</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11316,20 +11330,18 @@
         <v>86</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="M83" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="N83" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>75</v>
       </c>
@@ -11341,7 +11353,7 @@
         <v>75</v>
       </c>
       <c r="T83" t="s" s="2">
-        <v>417</v>
+        <v>75</v>
       </c>
       <c r="U83" t="s" s="2">
         <v>75</v>
@@ -11377,7 +11389,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11389,21 +11401,21 @@
         <v>97</v>
       </c>
       <c r="AJ83" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AK83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL83" t="s" s="2">
+      <c r="B84" t="s" s="2">
         <v>419</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11411,13 +11423,13 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>75</v>
@@ -11426,19 +11438,19 @@
         <v>86</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>258</v>
+        <v>420</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>75</v>
@@ -11451,7 +11463,7 @@
         <v>75</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>75</v>
+        <v>421</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>75</v>
@@ -11487,7 +11499,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -11499,21 +11511,21 @@
         <v>97</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>98</v>
+        <v>422</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>75</v>
+        <v>423</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11536,19 +11548,19 @@
         <v>86</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>267</v>
+        <v>376</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>75</v>
@@ -11597,7 +11609,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -11618,28 +11630,26 @@
         <v>75</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>75</v>
@@ -11648,19 +11658,19 @@
         <v>86</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>139</v>
+        <v>264</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>425</v>
+        <v>265</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>426</v>
+        <v>266</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>228</v>
+        <v>267</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>75</v>
@@ -11670,7 +11680,7 @@
         <v>75</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>360</v>
+        <v>75</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>75</v>
@@ -11685,11 +11695,13 @@
         <v>75</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y86" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z86" t="s" s="2">
-        <v>427</v>
+        <v>75</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>75</v>
@@ -11707,13 +11719,13 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>97</v>
@@ -11728,44 +11740,50 @@
         <v>75</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>428</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C87" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="D87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>101</v>
+        <v>429</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>75</v>
       </c>
@@ -11774,7 +11792,7 @@
         <v>75</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>75</v>
+        <v>364</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>75</v>
@@ -11789,13 +11807,11 @@
         <v>75</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
-        <v>75</v>
+        <v>431</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>75</v>
@@ -11813,19 +11829,19 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>75</v>
@@ -11836,21 +11852,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>75</v>
@@ -11862,17 +11878,15 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>75</v>
@@ -11909,31 +11923,31 @@
         <v>75</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>75</v>
@@ -11942,48 +11956,46 @@
         <v>75</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>75</v>
       </c>
@@ -12019,31 +12031,31 @@
         <v>75</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>75</v>
@@ -12052,9 +12064,9 @@
         <v>75</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>410</v>
@@ -12065,13 +12077,13 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>75</v>
@@ -12080,18 +12092,20 @@
         <v>86</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>75</v>
       </c>
@@ -12139,7 +12153,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12160,12 +12174,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12173,13 +12187,13 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>75</v>
@@ -12188,20 +12202,18 @@
         <v>86</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>75</v>
       </c>
@@ -12249,7 +12261,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -12270,12 +12282,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12283,13 +12295,13 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>75</v>
@@ -12298,19 +12310,19 @@
         <v>86</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>75</v>
@@ -12359,7 +12371,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -12382,10 +12394,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12408,19 +12420,19 @@
         <v>86</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>267</v>
+        <v>376</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>75</v>
@@ -12469,7 +12481,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -12492,10 +12504,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12518,19 +12530,19 @@
         <v>86</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>75</v>
@@ -12579,7 +12591,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -12600,26 +12612,26 @@
         <v>75</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>437</v>
+        <v>75</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>75</v>
@@ -12628,18 +12640,20 @@
         <v>86</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>438</v>
+        <v>100</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>439</v>
+        <v>272</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>440</v>
+        <v>273</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>75</v>
       </c>
@@ -12687,10 +12701,10 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>436</v>
+        <v>276</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>85</v>
@@ -12699,7 +12713,7 @@
         <v>97</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>327</v>
+        <v>98</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>75</v>
@@ -12710,18 +12724,18 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>75</v>
+        <v>441</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>85</v>
@@ -12745,7 +12759,7 @@
         <v>444</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>445</v>
+        <v>326</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12795,10 +12809,10 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>85</v>
@@ -12807,7 +12821,7 @@
         <v>97</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>75</v>
@@ -12816,12 +12830,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12829,7 +12843,7 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>85</v>
@@ -12844,16 +12858,16 @@
         <v>86</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -12891,17 +12905,19 @@
         <v>75</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AC97" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD97" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>452</v>
+        <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -12913,7 +12929,7 @@
         <v>97</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>75</v>
@@ -12924,26 +12940,24 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>75</v>
@@ -12952,16 +12966,16 @@
         <v>86</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -12999,19 +13013,17 @@
         <v>75</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="AC98" s="2"/>
       <c r="AD98" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>75</v>
+        <v>456</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -13029,18 +13041,18 @@
         <v>75</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>457</v>
+        <v>75</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C99" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>75</v>
@@ -13062,16 +13074,16 @@
         <v>86</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="L99" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>462</v>
-      </c>
       <c r="N99" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13121,7 +13133,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -13139,17 +13151,19 @@
         <v>75</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>75</v>
+        <v>461</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C100" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="B100" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>75</v>
       </c>
@@ -13179,7 +13193,7 @@
         <v>466</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>326</v>
+        <v>454</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13229,7 +13243,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -13241,7 +13255,7 @@
         <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>327</v>
+        <v>98</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>75</v>
@@ -13278,13 +13292,13 @@
         <v>86</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>326</v>
@@ -13349,7 +13363,7 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>75</v>
@@ -13360,10 +13374,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13374,7 +13388,7 @@
         <v>76</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>75</v>
@@ -13386,7 +13400,7 @@
         <v>86</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="L102" t="s" s="2">
         <v>472</v>
@@ -13394,7 +13408,9 @@
       <c r="M102" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N102" s="2"/>
+      <c r="N102" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>75</v>
@@ -13443,19 +13459,19 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>75</v>
@@ -13480,7 +13496,7 @@
         <v>76</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>75</v>
@@ -13489,16 +13505,16 @@
         <v>75</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>100</v>
+        <v>475</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>101</v>
+        <v>476</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>102</v>
+        <v>477</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13549,19 +13565,19 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>103</v>
+        <v>474</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>75</v>
@@ -13572,21 +13588,21 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>75</v>
@@ -13598,17 +13614,15 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>75</v>
@@ -13645,31 +13659,31 @@
         <v>75</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>75</v>
@@ -13680,14 +13694,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>477</v>
+        <v>105</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -13700,26 +13714,24 @@
         <v>75</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>478</v>
+        <v>107</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>479</v>
+        <v>108</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="O105" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>75</v>
       </c>
@@ -13755,19 +13767,19 @@
         <v>75</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>480</v>
+        <v>113</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -13790,33 +13802,33 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>75</v>
+        <v>481</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>214</v>
+        <v>106</v>
       </c>
       <c r="L106" t="s" s="2">
         <v>482</v>
@@ -13825,10 +13837,10 @@
         <v>483</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>349</v>
+        <v>109</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>484</v>
+        <v>304</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>75</v>
@@ -13853,13 +13865,13 @@
         <v>75</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>485</v>
+        <v>75</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>486</v>
+        <v>75</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>75</v>
@@ -13877,19 +13889,19 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>75</v>
@@ -13900,10 +13912,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13911,7 +13923,7 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>85</v>
@@ -13926,19 +13938,19 @@
         <v>86</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="O107" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>75</v>
@@ -13963,13 +13975,13 @@
         <v>75</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>75</v>
+        <v>489</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>75</v>
+        <v>490</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>75</v>
@@ -13987,10 +13999,10 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>85</v>
@@ -13999,7 +14011,7 @@
         <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>327</v>
+        <v>98</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>75</v>
@@ -14010,10 +14022,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14021,7 +14033,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>85</v>
@@ -14033,22 +14045,22 @@
         <v>75</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="M108" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>326</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>75</v>
@@ -14097,10 +14109,10 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>85</v>
@@ -14109,7 +14121,7 @@
         <v>97</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>75</v>
@@ -14120,10 +14132,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14143,22 +14155,22 @@
         <v>75</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>326</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>75</v>
@@ -14207,7 +14219,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -14219,7 +14231,7 @@
         <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>75</v>
@@ -14230,10 +14242,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14244,7 +14256,7 @@
         <v>76</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>75</v>
@@ -14256,7 +14268,7 @@
         <v>86</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>214</v>
+        <v>502</v>
       </c>
       <c r="L110" t="s" s="2">
         <v>503</v>
@@ -14265,9 +14277,11 @@
         <v>504</v>
       </c>
       <c r="N110" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="O110" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>75</v>
       </c>
@@ -14291,13 +14305,13 @@
         <v>75</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>506</v>
+        <v>75</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>507</v>
+        <v>75</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>75</v>
@@ -14315,19 +14329,19 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>75</v>
@@ -14336,12 +14350,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14355,7 +14369,7 @@
         <v>77</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>75</v>
@@ -14364,16 +14378,16 @@
         <v>86</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="N111" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14399,13 +14413,13 @@
         <v>75</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>75</v>
+        <v>510</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>75</v>
+        <v>511</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>75</v>
@@ -14423,7 +14437,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -14435,7 +14449,7 @@
         <v>97</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>327</v>
+        <v>98</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>75</v>
@@ -14446,10 +14460,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14472,7 +14486,7 @@
         <v>86</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>214</v>
+        <v>513</v>
       </c>
       <c r="L112" t="s" s="2">
         <v>514</v>
@@ -14507,13 +14521,13 @@
         <v>75</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>517</v>
+        <v>75</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>518</v>
+        <v>75</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>75</v>
@@ -14531,7 +14545,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -14543,7 +14557,7 @@
         <v>97</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>75</v>
@@ -14552,12 +14566,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14568,27 +14582,29 @@
         <v>76</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>101</v>
+        <v>518</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>75</v>
@@ -14613,13 +14629,13 @@
         <v>75</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>75</v>
+        <v>521</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>75</v>
+        <v>522</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>75</v>
@@ -14637,19 +14653,19 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>103</v>
+        <v>517</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>75</v>
@@ -14660,21 +14676,21 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>75</v>
@@ -14686,17 +14702,15 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>75</v>
@@ -14733,31 +14747,31 @@
         <v>75</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC114" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD114" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>75</v>
@@ -14768,14 +14782,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -14785,29 +14799,27 @@
         <v>77</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>226</v>
+        <v>107</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>227</v>
+        <v>108</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>75</v>
       </c>
@@ -14843,9 +14855,11 @@
         <v>75</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AC115" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="AD115" t="s" s="2">
         <v>75</v>
       </c>
@@ -14853,7 +14867,7 @@
         <v>112</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -14865,7 +14879,7 @@
         <v>97</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>75</v>
@@ -14874,16 +14888,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>75</v>
       </c>
@@ -14892,7 +14904,7 @@
         <v>76</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>86</v>
@@ -14907,10 +14919,10 @@
         <v>139</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>358</v>
+        <v>226</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>359</v>
+        <v>227</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>228</v>
@@ -14953,16 +14965,14 @@
         <v>75</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>526</v>
+      </c>
+      <c r="AC116" s="2"/>
       <c r="AD116" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF116" t="s" s="2">
         <v>230</v>
@@ -14986,14 +14996,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B117" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="B117" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="C117" s="2"/>
+      <c r="C117" t="s" s="2">
+        <v>528</v>
+      </c>
       <c r="D117" t="s" s="2">
         <v>75</v>
       </c>
@@ -15005,25 +15017,29 @@
         <v>85</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>101</v>
+        <v>362</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>75</v>
       </c>
@@ -15071,19 +15087,19 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>75</v>
@@ -15094,21 +15110,21 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>75</v>
@@ -15120,17 +15136,15 @@
         <v>75</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>75</v>
@@ -15167,31 +15181,31 @@
         <v>75</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>75</v>
@@ -15200,48 +15214,46 @@
         <v>75</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>75</v>
       </c>
@@ -15250,7 +15262,7 @@
         <v>75</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>531</v>
+        <v>75</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>75</v>
@@ -15277,31 +15289,31 @@
         <v>75</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>75</v>
@@ -15312,10 +15324,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15323,7 +15335,7 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G120" t="s" s="2">
         <v>85</v>
@@ -15338,18 +15350,20 @@
         <v>86</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O120" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>75</v>
       </c>
@@ -15358,7 +15372,7 @@
         <v>75</v>
       </c>
       <c r="S120" t="s" s="2">
-        <v>75</v>
+        <v>535</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>75</v>
@@ -15397,7 +15411,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -15420,10 +15434,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15431,7 +15445,7 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G121" t="s" s="2">
         <v>85</v>
@@ -15446,20 +15460,18 @@
         <v>86</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>75</v>
       </c>
@@ -15507,7 +15519,7 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
@@ -15528,12 +15540,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15541,13 +15553,13 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G122" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>75</v>
@@ -15556,19 +15568,19 @@
         <v>86</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>75</v>
@@ -15617,7 +15629,7 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -15640,10 +15652,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15666,19 +15678,19 @@
         <v>86</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>267</v>
+        <v>376</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>75</v>
@@ -15727,7 +15739,7 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -15750,10 +15762,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15776,19 +15788,19 @@
         <v>86</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>75</v>
@@ -15837,7 +15849,7 @@
         <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -15858,12 +15870,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15877,7 +15889,7 @@
         <v>85</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>75</v>
@@ -15886,18 +15898,20 @@
         <v>86</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>214</v>
+        <v>100</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>542</v>
+        <v>272</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>543</v>
+        <v>273</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O125" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P125" t="s" s="2">
         <v>75</v>
       </c>
@@ -15921,11 +15935,13 @@
         <v>75</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y125" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z125" t="s" s="2">
-        <v>545</v>
+        <v>75</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>75</v>
@@ -15943,7 +15959,7 @@
         <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>541</v>
+        <v>276</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -15961,15 +15977,15 @@
         <v>75</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>546</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15983,24 +15999,26 @@
         <v>85</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>101</v>
+        <v>546</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N126" s="2"/>
+        <v>547</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>75</v>
@@ -16025,13 +16043,11 @@
         <v>75</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Y126" s="2"/>
       <c r="Z126" t="s" s="2">
-        <v>75</v>
+        <v>549</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>75</v>
@@ -16049,7 +16065,7 @@
         <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>103</v>
+        <v>545</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>76</v>
@@ -16058,35 +16074,35 @@
         <v>85</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>75</v>
+        <v>550</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>75</v>
@@ -16098,17 +16114,15 @@
         <v>75</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>75</v>
@@ -16145,31 +16159,31 @@
         <v>75</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC127" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>75</v>
@@ -16180,14 +16194,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -16203,23 +16217,21 @@
         <v>75</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>550</v>
+        <v>107</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>551</v>
+        <v>108</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>75</v>
       </c>
@@ -16255,19 +16267,19 @@
         <v>75</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
@@ -16279,7 +16291,7 @@
         <v>75</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>75</v>
@@ -16290,10 +16302,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16304,7 +16316,7 @@
         <v>76</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>75</v>
@@ -16313,19 +16325,23 @@
         <v>75</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>101</v>
+        <v>554</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
+        <v>555</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>75</v>
       </c>
@@ -16373,19 +16389,19 @@
         <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>75</v>
@@ -16396,21 +16412,21 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>75</v>
@@ -16422,17 +16438,15 @@
         <v>75</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>75</v>
@@ -16469,31 +16483,31 @@
         <v>75</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>75</v>
@@ -16502,48 +16516,46 @@
         <v>75</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>75</v>
       </c>
@@ -16552,7 +16564,7 @@
         <v>75</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>555</v>
+        <v>75</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>75</v>
@@ -16579,31 +16591,31 @@
         <v>75</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>75</v>
@@ -16612,12 +16624,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="132" hidden="true">
+    <row r="132">
       <c r="A132" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16631,7 +16643,7 @@
         <v>85</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>75</v>
@@ -16640,18 +16652,20 @@
         <v>86</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O132" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>75</v>
       </c>
@@ -16660,7 +16674,7 @@
         <v>75</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>75</v>
+        <v>559</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>75</v>
@@ -16699,7 +16713,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -16720,12 +16734,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16739,7 +16753,7 @@
         <v>85</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>75</v>
@@ -16748,18 +16762,18 @@
         <v>86</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>75</v>
       </c>
@@ -16807,7 +16821,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -16828,12 +16842,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="134" hidden="true">
+    <row r="134">
       <c r="A134" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16847,7 +16861,7 @@
         <v>85</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>75</v>
@@ -16856,17 +16870,17 @@
         <v>86</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>75</v>
@@ -16915,7 +16929,7 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -16938,10 +16952,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16964,19 +16978,17 @@
         <v>86</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N135" s="2"/>
       <c r="O135" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>75</v>
@@ -17025,7 +17037,7 @@
         <v>75</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -17048,10 +17060,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17074,19 +17086,19 @@
         <v>86</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>75</v>
@@ -17135,7 +17147,7 @@
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>76</v>
@@ -17158,10 +17170,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17172,7 +17184,7 @@
         <v>76</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>75</v>
@@ -17181,21 +17193,23 @@
         <v>75</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>562</v>
+        <v>100</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>563</v>
+        <v>272</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>564</v>
+        <v>273</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="O137" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P137" t="s" s="2">
         <v>75</v>
       </c>
@@ -17243,19 +17257,19 @@
         <v>75</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>561</v>
+        <v>276</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>327</v>
+        <v>98</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>75</v>
@@ -17266,10 +17280,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17283,7 +17297,7 @@
         <v>77</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I138" t="s" s="2">
         <v>75</v>
@@ -17292,7 +17306,7 @@
         <v>75</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>214</v>
+        <v>566</v>
       </c>
       <c r="L138" t="s" s="2">
         <v>567</v>
@@ -17327,29 +17341,31 @@
         <v>75</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>570</v>
+        <v>75</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>571</v>
+        <v>75</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AC138" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD138" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>76</v>
@@ -17361,25 +17377,23 @@
         <v>97</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>572</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="C139" t="s" s="2">
-        <v>574</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
         <v>75</v>
       </c>
@@ -17403,13 +17417,13 @@
         <v>214</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -17435,9 +17449,11 @@
         <v>75</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y139" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>574</v>
+      </c>
       <c r="Z139" t="s" s="2">
         <v>575</v>
       </c>
@@ -17445,19 +17461,17 @@
         <v>75</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="AC139" s="2"/>
       <c r="AD139" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>76</v>
@@ -17475,17 +17489,19 @@
         <v>75</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>75</v>
+        <v>576</v>
       </c>
     </row>
-    <row r="140" hidden="true">
+    <row r="140">
       <c r="A140" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C140" s="2"/>
+        <v>570</v>
+      </c>
+      <c r="C140" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="D140" t="s" s="2">
         <v>75</v>
       </c>
@@ -17494,10 +17510,10 @@
         <v>76</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I140" t="s" s="2">
         <v>75</v>
@@ -17506,15 +17522,17 @@
         <v>75</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>101</v>
+        <v>571</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N140" s="2"/>
+        <v>572</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>573</v>
+      </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>75</v>
@@ -17539,13 +17557,11 @@
         <v>75</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Y140" s="2"/>
       <c r="Z140" t="s" s="2">
-        <v>75</v>
+        <v>579</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>75</v>
@@ -17563,19 +17579,19 @@
         <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>103</v>
+        <v>570</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>75</v>
@@ -17586,21 +17602,21 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>75</v>
@@ -17612,17 +17628,15 @@
         <v>75</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>75</v>
@@ -17659,31 +17673,31 @@
         <v>75</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>75</v>
@@ -17694,14 +17708,14 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -17717,23 +17731,21 @@
         <v>75</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>582</v>
+        <v>107</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>583</v>
+        <v>108</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>75</v>
       </c>
@@ -17769,19 +17781,19 @@
         <v>75</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>76</v>
@@ -17793,7 +17805,7 @@
         <v>75</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>75</v>
@@ -17818,7 +17830,7 @@
         <v>76</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>75</v>
@@ -17827,19 +17839,23 @@
         <v>75</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>101</v>
+        <v>586</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N143" s="2"/>
-      <c r="O143" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P143" t="s" s="2">
         <v>75</v>
       </c>
@@ -17887,19 +17903,19 @@
         <v>75</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>75</v>
@@ -17910,21 +17926,21 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>75</v>
@@ -17936,17 +17952,15 @@
         <v>75</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>75</v>
@@ -17983,31 +17997,31 @@
         <v>75</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC144" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD144" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>75</v>
@@ -18018,21 +18032,21 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>75</v>
@@ -18041,23 +18055,21 @@
         <v>75</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>75</v>
       </c>
@@ -18066,7 +18078,7 @@
         <v>75</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>590</v>
+        <v>75</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>75</v>
@@ -18093,31 +18105,31 @@
         <v>75</v>
       </c>
       <c r="AB145" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC145" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD145" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE145" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>75</v>
@@ -18128,10 +18140,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18154,18 +18166,20 @@
         <v>86</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O146" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O146" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P146" t="s" s="2">
         <v>75</v>
       </c>
@@ -18174,7 +18188,7 @@
         <v>75</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>75</v>
+        <v>594</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>75</v>
@@ -18213,7 +18227,7 @@
         <v>75</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>76</v>
@@ -18234,12 +18248,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18247,13 +18261,13 @@
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G147" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>75</v>
@@ -18262,18 +18276,18 @@
         <v>86</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N147" s="2"/>
-      <c r="O147" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>75</v>
       </c>
@@ -18321,7 +18335,7 @@
         <v>75</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>76</v>
@@ -18342,12 +18356,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="148" hidden="true">
+    <row r="148">
       <c r="A148" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -18355,13 +18369,13 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G148" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H148" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I148" t="s" s="2">
         <v>75</v>
@@ -18370,17 +18384,17 @@
         <v>86</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>75</v>
@@ -18429,7 +18443,7 @@
         <v>75</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>76</v>
@@ -18452,10 +18466,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18478,19 +18492,17 @@
         <v>86</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>75</v>
@@ -18539,7 +18551,7 @@
         <v>75</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>76</v>
@@ -18562,10 +18574,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18588,19 +18600,19 @@
         <v>86</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>75</v>
@@ -18649,7 +18661,7 @@
         <v>75</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>76</v>
@@ -18670,16 +18682,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="C151" t="s" s="2">
-        <v>602</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
         <v>75</v>
       </c>
@@ -18688,30 +18698,32 @@
         <v>76</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H151" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J151" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I151" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J151" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="K151" t="s" s="2">
-        <v>214</v>
+        <v>100</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>567</v>
+        <v>272</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>568</v>
+        <v>273</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="O151" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="O151" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P151" t="s" s="2">
         <v>75</v>
       </c>
@@ -18735,11 +18747,13 @@
         <v>75</v>
       </c>
       <c r="X151" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="Y151" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z151" t="s" s="2">
-        <v>603</v>
+        <v>75</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>75</v>
@@ -18757,16 +18771,16 @@
         <v>75</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>566</v>
+        <v>276</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>98</v>
@@ -18778,14 +18792,16 @@
         <v>75</v>
       </c>
     </row>
-    <row r="152" hidden="true">
+    <row r="152">
       <c r="A152" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C152" s="2"/>
+        <v>570</v>
+      </c>
+      <c r="C152" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="D152" t="s" s="2">
         <v>75</v>
       </c>
@@ -18794,10 +18810,10 @@
         <v>76</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>75</v>
@@ -18806,15 +18822,17 @@
         <v>75</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>100</v>
+        <v>214</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>101</v>
+        <v>571</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N152" s="2"/>
+        <v>572</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>573</v>
+      </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>75</v>
@@ -18839,13 +18857,11 @@
         <v>75</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Y152" s="2"/>
       <c r="Z152" t="s" s="2">
-        <v>75</v>
+        <v>607</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>75</v>
@@ -18863,19 +18879,19 @@
         <v>75</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>103</v>
+        <v>570</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>75</v>
@@ -18886,21 +18902,21 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>75</v>
@@ -18912,17 +18928,15 @@
         <v>75</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>75</v>
@@ -18959,31 +18973,31 @@
         <v>75</v>
       </c>
       <c r="AB153" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC153" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD153" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE153" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>75</v>
@@ -18994,14 +19008,14 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -19017,23 +19031,21 @@
         <v>75</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>607</v>
+        <v>107</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>608</v>
+        <v>108</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>75</v>
       </c>
@@ -19069,19 +19081,19 @@
         <v>75</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>76</v>
@@ -19093,7 +19105,7 @@
         <v>75</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>75</v>
@@ -19104,7 +19116,7 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>585</v>
@@ -19118,7 +19130,7 @@
         <v>76</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>75</v>
@@ -19127,19 +19139,23 @@
         <v>75</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>101</v>
+        <v>611</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N155" s="2"/>
-      <c r="O155" s="2"/>
+        <v>612</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P155" t="s" s="2">
         <v>75</v>
       </c>
@@ -19187,19 +19203,19 @@
         <v>75</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK155" t="s" s="2">
         <v>75</v>
@@ -19210,21 +19226,21 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>75</v>
@@ -19236,17 +19252,15 @@
         <v>75</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N156" s="2"/>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>75</v>
@@ -19283,31 +19297,31 @@
         <v>75</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>75</v>
@@ -19318,21 +19332,21 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>75</v>
@@ -19341,23 +19355,21 @@
         <v>75</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>75</v>
       </c>
@@ -19366,7 +19378,7 @@
         <v>75</v>
       </c>
       <c r="S157" t="s" s="2">
-        <v>612</v>
+        <v>75</v>
       </c>
       <c r="T157" t="s" s="2">
         <v>75</v>
@@ -19393,31 +19405,31 @@
         <v>75</v>
       </c>
       <c r="AB157" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC157" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD157" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE157" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>75</v>
@@ -19428,10 +19440,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -19439,7 +19451,7 @@
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G158" t="s" s="2">
         <v>85</v>
@@ -19454,18 +19466,20 @@
         <v>86</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O158" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P158" t="s" s="2">
         <v>75</v>
       </c>
@@ -19474,7 +19488,7 @@
         <v>75</v>
       </c>
       <c r="S158" t="s" s="2">
-        <v>75</v>
+        <v>616</v>
       </c>
       <c r="T158" t="s" s="2">
         <v>75</v>
@@ -19513,7 +19527,7 @@
         <v>75</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>76</v>
@@ -19536,10 +19550,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19547,7 +19561,7 @@
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G159" t="s" s="2">
         <v>85</v>
@@ -19562,18 +19576,18 @@
         <v>86</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N159" s="2"/>
-      <c r="O159" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
         <v>75</v>
       </c>
@@ -19621,7 +19635,7 @@
         <v>75</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>76</v>
@@ -19644,10 +19658,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -19655,7 +19669,7 @@
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G160" t="s" s="2">
         <v>85</v>
@@ -19670,17 +19684,17 @@
         <v>86</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>75</v>
@@ -19729,7 +19743,7 @@
         <v>75</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>76</v>
@@ -19752,10 +19766,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -19778,19 +19792,17 @@
         <v>86</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>75</v>
@@ -19839,7 +19851,7 @@
         <v>75</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>76</v>
@@ -19862,10 +19874,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19888,19 +19900,19 @@
         <v>86</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>75</v>
@@ -19949,7 +19961,7 @@
         <v>75</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>76</v>
@@ -19972,10 +19984,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -19986,7 +19998,7 @@
         <v>76</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>75</v>
@@ -19995,22 +20007,22 @@
         <v>75</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>619</v>
+        <v>100</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>620</v>
+        <v>272</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>621</v>
+        <v>273</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>326</v>
+        <v>274</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>622</v>
+        <v>275</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>75</v>
@@ -20059,19 +20071,19 @@
         <v>75</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>618</v>
+        <v>276</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>327</v>
+        <v>98</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>75</v>
@@ -20082,10 +20094,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20108,7 +20120,7 @@
         <v>75</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>214</v>
+        <v>623</v>
       </c>
       <c r="L164" t="s" s="2">
         <v>624</v>
@@ -20117,9 +20129,11 @@
         <v>625</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O164" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>626</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>75</v>
       </c>
@@ -20143,13 +20157,13 @@
         <v>75</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>626</v>
+        <v>75</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>627</v>
+        <v>75</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>75</v>
@@ -20167,7 +20181,7 @@
         <v>75</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>76</v>
@@ -20179,7 +20193,7 @@
         <v>97</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="AK164" t="s" s="2">
         <v>75</v>
@@ -20188,12 +20202,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20207,7 +20221,7 @@
         <v>77</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>75</v>
@@ -20216,16 +20230,16 @@
         <v>75</v>
       </c>
       <c r="K165" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L165" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="L165" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>631</v>
-      </c>
       <c r="N165" t="s" s="2">
-        <v>632</v>
+        <v>353</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -20251,13 +20265,13 @@
         <v>75</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>75</v>
+        <v>630</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>75</v>
+        <v>631</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>75</v>
@@ -20275,7 +20289,7 @@
         <v>75</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>76</v>
@@ -20296,12 +20310,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="166" hidden="true">
+    <row r="166">
       <c r="A166" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20315,7 +20329,7 @@
         <v>77</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>75</v>
@@ -20324,7 +20338,7 @@
         <v>75</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>471</v>
+        <v>633</v>
       </c>
       <c r="L166" t="s" s="2">
         <v>634</v>
@@ -20332,7 +20346,9 @@
       <c r="M166" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="N166" s="2"/>
+      <c r="N166" t="s" s="2">
+        <v>636</v>
+      </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>75</v>
@@ -20381,7 +20397,7 @@
         <v>75</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>76</v>
@@ -20404,10 +20420,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -20418,7 +20434,7 @@
         <v>76</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>75</v>
@@ -20430,13 +20446,13 @@
         <v>75</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>100</v>
+        <v>475</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>101</v>
+        <v>638</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>102</v>
+        <v>639</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -20487,19 +20503,19 @@
         <v>75</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>103</v>
+        <v>637</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>75</v>
@@ -20510,21 +20526,21 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>75</v>
@@ -20536,17 +20552,15 @@
         <v>75</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>109</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N168" s="2"/>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>75</v>
@@ -20583,31 +20597,31 @@
         <v>75</v>
       </c>
       <c r="AB168" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AC168" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AD168" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE168" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>75</v>
@@ -20618,14 +20632,14 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>477</v>
+        <v>105</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -20638,26 +20652,24 @@
         <v>75</v>
       </c>
       <c r="I169" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K169" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>478</v>
+        <v>107</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>479</v>
+        <v>108</v>
       </c>
       <c r="N169" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="O169" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>75</v>
       </c>
@@ -20693,19 +20705,19 @@
         <v>75</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>480</v>
+        <v>113</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>76</v>
@@ -20728,44 +20740,46 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>75</v>
+        <v>481</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H170" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I170" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J170" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>214</v>
+        <v>106</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>640</v>
+        <v>482</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>641</v>
+        <v>483</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O170" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="O170" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P170" t="s" s="2">
         <v>75</v>
       </c>
@@ -20789,13 +20803,13 @@
         <v>75</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>642</v>
+        <v>75</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>643</v>
+        <v>75</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>75</v>
@@ -20813,19 +20827,19 @@
         <v>75</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>639</v>
+        <v>484</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI170" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>75</v>
@@ -20836,10 +20850,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -20847,7 +20861,7 @@
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G171" t="s" s="2">
         <v>85</v>
@@ -20862,16 +20876,16 @@
         <v>75</v>
       </c>
       <c r="K171" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L171" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="L171" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>647</v>
-      </c>
       <c r="N171" t="s" s="2">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -20897,13 +20911,13 @@
         <v>75</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>75</v>
+        <v>646</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>75</v>
+        <v>647</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>75</v>
@@ -20921,10 +20935,10 @@
         <v>75</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AG171" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH171" t="s" s="2">
         <v>85</v>
@@ -20933,7 +20947,7 @@
         <v>97</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>327</v>
+        <v>98</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>75</v>
@@ -20955,10 +20969,10 @@
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>75</v>
@@ -20979,11 +20993,9 @@
         <v>651</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>653</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>75</v>
       </c>
@@ -21034,16 +21046,16 @@
         <v>648</v>
       </c>
       <c r="AG172" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH172" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI172" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK172" t="s" s="2">
         <v>75</v>
@@ -21054,10 +21066,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -21080,18 +21092,20 @@
         <v>75</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>214</v>
+        <v>653</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="M173" t="s" s="2">
+      <c r="N173" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="N173" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="O173" s="2"/>
+      <c r="O173" t="s" s="2">
+        <v>657</v>
+      </c>
       <c r="P173" t="s" s="2">
         <v>75</v>
       </c>
@@ -21115,13 +21129,13 @@
         <v>75</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>657</v>
+        <v>75</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>658</v>
+        <v>75</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>75</v>
@@ -21139,7 +21153,7 @@
         <v>75</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>76</v>
@@ -21151,17 +21165,125 @@
         <v>97</v>
       </c>
       <c r="AJ173" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AK173" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL173" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="174" hidden="true">
+      <c r="A174" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C174" s="2"/>
+      <c r="D174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E174" s="2"/>
+      <c r="F174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G174" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K174" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L174" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="M174" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="O174" s="2"/>
+      <c r="P174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q174" s="2"/>
+      <c r="R174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X174" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y174" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="Z174" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AA174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF174" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AG174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH174" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI174" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ174" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="AK173" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL173" t="s" s="2">
+      <c r="AK174" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL174" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL173">
+  <autoFilter ref="A1:AL174">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -21171,7 +21293,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI172">
+  <conditionalFormatting sqref="A2:AI173">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:16:47+00:00</t>
+    <t>2026-08-28T12:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5981" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5980" uniqueCount="663">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1287,10 +1287,10 @@
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>Seitenlokalisation (OPS-Seitenzusatz R/L/B)</t>
+  </si>
+  <si>
+    <t>Seitenangabe bei paarigen Organen und OPS-Codes mit Seitenzusatzpflicht über die Basisprofil-Extension seitenlokalisation (R/L/B). Das oBDS sieht am OP kein eigenes Seitenfeld vor; führend ist der OPS-Seitenzusatz.</t>
   </si>
   <si>
     <t>Procedure.code.coding:ops.system</t>
@@ -11093,7 +11093,7 @@
         <v>405</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11120,9 +11120,7 @@
       <c r="M81" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="N81" t="s" s="2">
-        <v>109</v>
-      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>75</v>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$212</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$213</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7871" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7912" uniqueCount="789">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1483,6 +1483,9 @@
   </si>
   <si>
     <t>Procedure.code.coding.extension.value[x].code</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Procedure.code.coding:ops.extension:Seitenlokalisation.value[x].display</t>
@@ -2020,6 +2023,22 @@
   </si>
   <si>
     <t>Procedure.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension:bodySite</t>
+  </si>
+  <si>
+    <t>bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {bodySite}
+</t>
+  </si>
+  <si>
+    <t>Target anatomic location or structure</t>
+  </si>
+  <si>
+    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
   </si>
   <si>
     <t>Procedure.bodySite.coding</t>
@@ -2756,7 +2775,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO212"/>
+  <dimension ref="A1:AO213"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.5703125" customWidth="true" bestFit="true"/>
@@ -5116,7 +5135,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>117</v>
@@ -5348,7 +5367,7 @@
         <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>101</v>
@@ -13873,7 +13892,7 @@
         <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>117</v>
@@ -14222,7 +14241,7 @@
         <v>80</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>117</v>
@@ -14452,7 +14471,7 @@
         <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>101</v>
@@ -14684,7 +14703,7 @@
         <v>80</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>117</v>
@@ -14803,7 +14822,7 @@
         <v>89</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>101</v>
@@ -14920,7 +14939,7 @@
         <v>89</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>101</v>
@@ -14977,7 +14996,9 @@
       <c r="M105" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="N105" s="2"/>
+      <c r="N105" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="O105" t="s" s="2">
         <v>248</v>
       </c>
@@ -15037,7 +15058,7 @@
         <v>89</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>101</v>
@@ -15060,10 +15081,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15094,7 +15115,9 @@
       <c r="M106" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="N106" s="2"/>
+      <c r="N106" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="O106" t="s" s="2">
         <v>255</v>
       </c>
@@ -15154,7 +15177,7 @@
         <v>89</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>101</v>
@@ -15177,10 +15200,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15273,7 +15296,7 @@
         <v>89</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>101</v>
@@ -15296,10 +15319,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15325,7 +15348,7 @@
         <v>130</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M108" t="s" s="2">
         <v>231</v>
@@ -15341,7 +15364,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>78</v>
@@ -15392,7 +15415,7 @@
         <v>89</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>101</v>
@@ -15415,10 +15438,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15444,10 +15467,10 @@
         <v>103</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>241</v>
@@ -15509,7 +15532,7 @@
         <v>89</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>101</v>
@@ -15518,7 +15541,7 @@
         <v>78</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -15532,10 +15555,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15561,12 +15584,14 @@
         <v>164</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M110" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="N110" s="2"/>
+      <c r="N110" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="O110" t="s" s="2">
         <v>248</v>
       </c>
@@ -15581,7 +15606,7 @@
         <v>78</v>
       </c>
       <c r="T110" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="U110" t="s" s="2">
         <v>78</v>
@@ -15626,16 +15651,16 @@
         <v>89</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -15649,10 +15674,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15683,7 +15708,9 @@
       <c r="M111" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="N111" s="2"/>
+      <c r="N111" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="O111" t="s" s="2">
         <v>255</v>
       </c>
@@ -15743,7 +15770,7 @@
         <v>89</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>101</v>
@@ -15766,10 +15793,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15862,7 +15889,7 @@
         <v>89</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>101</v>
@@ -15885,7 +15912,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>436</v>
@@ -15916,10 +15943,10 @@
         <v>142</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>285</v>
@@ -15954,7 +15981,7 @@
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>78</v>
@@ -16004,7 +16031,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>445</v>
@@ -16119,7 +16146,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>447</v>
@@ -16236,10 +16263,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16355,10 +16382,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16472,10 +16499,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16589,10 +16616,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16706,10 +16733,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16825,10 +16852,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16944,14 +16971,14 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -16970,13 +16997,13 @@
         <v>90</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17027,7 +17054,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>89</v>
@@ -17048,21 +17075,21 @@
         <v>78</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17174,10 +17201,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17291,10 +17318,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17320,13 +17347,13 @@
         <v>103</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17376,7 +17403,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17385,7 +17412,7 @@
         <v>89</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>101</v>
@@ -17408,10 +17435,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17437,13 +17464,13 @@
         <v>130</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -17472,10 +17499,10 @@
         <v>146</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>78</v>
@@ -17493,7 +17520,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17525,10 +17552,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17554,13 +17581,13 @@
         <v>343</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17610,7 +17637,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17642,10 +17669,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17671,13 +17698,13 @@
         <v>103</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -17727,7 +17754,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17759,10 +17786,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17785,16 +17812,16 @@
         <v>90</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -17844,7 +17871,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17865,21 +17892,21 @@
         <v>78</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17991,10 +18018,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18108,10 +18135,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18137,13 +18164,13 @@
         <v>103</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18193,7 +18220,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18202,7 +18229,7 @@
         <v>89</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>101</v>
@@ -18225,10 +18252,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18254,13 +18281,13 @@
         <v>130</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18289,10 +18316,10 @@
         <v>146</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>78</v>
@@ -18310,7 +18337,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18342,10 +18369,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18371,13 +18398,13 @@
         <v>343</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18427,7 +18454,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18459,10 +18486,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18488,13 +18515,13 @@
         <v>103</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18544,7 +18571,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18576,10 +18603,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18605,13 +18632,13 @@
         <v>208</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18649,17 +18676,17 @@
         <v>78</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AC136" s="2"/>
       <c r="AD136" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18680,24 +18707,24 @@
         <v>78</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>78</v>
@@ -18722,13 +18749,13 @@
         <v>208</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -18778,7 +18805,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18796,27 +18823,27 @@
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>78</v>
@@ -18838,16 +18865,16 @@
         <v>90</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -18897,7 +18924,7 @@
         <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -18918,21 +18945,21 @@
         <v>78</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18955,13 +18982,13 @@
         <v>90</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19012,7 +19039,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -19036,7 +19063,7 @@
         <v>78</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>78</v>
@@ -19044,10 +19071,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19070,13 +19097,13 @@
         <v>90</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19127,7 +19154,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19151,7 +19178,7 @@
         <v>78</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>78</v>
@@ -19159,10 +19186,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19185,13 +19212,13 @@
         <v>90</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -19242,7 +19269,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19263,7 +19290,7 @@
         <v>78</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>78</v>
@@ -19274,10 +19301,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19389,10 +19416,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19506,14 +19533,14 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -19535,10 +19562,10 @@
         <v>109</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>112</v>
@@ -19593,7 +19620,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -19625,10 +19652,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19654,14 +19681,14 @@
         <v>277</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -19689,10 +19716,10 @@
         <v>154</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>78</v>
@@ -19710,7 +19737,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -19731,21 +19758,21 @@
         <v>78</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO145" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19768,17 +19795,17 @@
         <v>90</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>78</v>
@@ -19827,7 +19854,7 @@
         <v>78</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>89</v>
@@ -19848,21 +19875,21 @@
         <v>78</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19885,17 +19912,17 @@
         <v>78</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>78</v>
@@ -19944,7 +19971,7 @@
         <v>78</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -19976,10 +20003,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20002,17 +20029,17 @@
         <v>90</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>78</v>
@@ -20061,7 +20088,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20085,7 +20112,7 @@
         <v>78</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>78</v>
@@ -20093,10 +20120,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20122,13 +20149,13 @@
         <v>277</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -20157,10 +20184,10 @@
         <v>154</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>78</v>
@@ -20178,7 +20205,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20199,10 +20226,10 @@
         <v>78</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>78</v>
@@ -20210,10 +20237,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20236,16 +20263,16 @@
         <v>90</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20295,7 +20322,7 @@
         <v>78</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -20316,10 +20343,10 @@
         <v>78</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>78</v>
@@ -20327,10 +20354,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20356,13 +20383,13 @@
         <v>277</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20391,10 +20418,10 @@
         <v>154</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>78</v>
@@ -20412,7 +20439,7 @@
         <v>78</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -20439,15 +20466,15 @@
         <v>78</v>
       </c>
       <c r="AO151" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20559,10 +20586,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20676,12 +20703,14 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="C154" s="2"/>
+      <c r="C154" t="s" s="2">
+        <v>647</v>
+      </c>
       <c r="D154" t="s" s="2">
         <v>78</v>
       </c>
@@ -20690,32 +20719,28 @@
         <v>79</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H154" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I154" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>142</v>
+        <v>648</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>283</v>
+        <v>649</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="N154" s="2"/>
+      <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>78</v>
       </c>
@@ -20751,17 +20776,19 @@
         <v>78</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="AC154" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD154" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -20773,7 +20800,7 @@
         <v>78</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>78</v>
@@ -20788,19 +20815,17 @@
         <v>78</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="C155" t="s" s="2">
-        <v>648</v>
-      </c>
+        <v>651</v>
+      </c>
+      <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
         <v>78</v>
       </c>
@@ -20809,7 +20834,7 @@
         <v>79</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>90</v>
@@ -20824,10 +20849,10 @@
         <v>142</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>405</v>
+        <v>283</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>406</v>
+        <v>284</v>
       </c>
       <c r="N155" t="s" s="2">
         <v>285</v>
@@ -20870,16 +20895,14 @@
         <v>78</v>
       </c>
       <c r="AB155" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>652</v>
+      </c>
+      <c r="AC155" s="2"/>
       <c r="AD155" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE155" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF155" t="s" s="2">
         <v>287</v>
@@ -20912,14 +20935,16 @@
         <v>288</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="C156" s="2"/>
+        <v>651</v>
+      </c>
+      <c r="C156" t="s" s="2">
+        <v>654</v>
+      </c>
       <c r="D156" t="s" s="2">
         <v>78</v>
       </c>
@@ -20931,25 +20956,29 @@
         <v>89</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>104</v>
+        <v>405</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N156" s="2"/>
-      <c r="O156" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O156" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P156" t="s" s="2">
         <v>78</v>
       </c>
@@ -20997,19 +21026,19 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>78</v>
@@ -21024,26 +21053,26 @@
         <v>78</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>78</v>
@@ -21055,17 +21084,15 @@
         <v>78</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N157" s="2"/>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>78</v>
@@ -21102,31 +21129,31 @@
         <v>78</v>
       </c>
       <c r="AB157" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC157" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD157" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE157" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>78</v>
@@ -21144,48 +21171,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H158" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I158" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>78</v>
       </c>
@@ -21194,7 +21219,7 @@
         <v>78</v>
       </c>
       <c r="S158" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="T158" t="s" s="2">
         <v>78</v>
@@ -21221,31 +21246,31 @@
         <v>78</v>
       </c>
       <c r="AB158" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC158" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD158" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE158" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI158" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>78</v>
@@ -21260,15 +21285,15 @@
         <v>78</v>
       </c>
       <c r="AO158" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21276,7 +21301,7 @@
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G159" t="s" s="2">
         <v>89</v>
@@ -21291,18 +21316,20 @@
         <v>90</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O159" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O159" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
       </c>
@@ -21311,7 +21338,7 @@
         <v>78</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>78</v>
@@ -21350,7 +21377,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21377,15 +21404,15 @@
         <v>78</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21393,7 +21420,7 @@
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G160" t="s" s="2">
         <v>89</v>
@@ -21408,18 +21435,18 @@
         <v>90</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>78</v>
       </c>
@@ -21467,7 +21494,7 @@
         <v>78</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -21494,15 +21521,15 @@
         <v>78</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
-    <row r="161" hidden="true">
+    <row r="161">
       <c r="A161" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21510,13 +21537,13 @@
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G161" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>78</v>
@@ -21525,17 +21552,17 @@
         <v>90</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>78</v>
@@ -21584,7 +21611,7 @@
         <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -21611,15 +21638,15 @@
         <v>78</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21642,19 +21669,17 @@
         <v>90</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>78</v>
@@ -21703,7 +21728,7 @@
         <v>78</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -21730,15 +21755,15 @@
         <v>78</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21761,19 +21786,19 @@
         <v>90</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>78</v>
@@ -21822,7 +21847,7 @@
         <v>78</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -21849,15 +21874,15 @@
         <v>78</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>312</v>
+        <v>266</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21871,7 +21896,7 @@
         <v>89</v>
       </c>
       <c r="H164" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I164" t="s" s="2">
         <v>78</v>
@@ -21880,18 +21905,20 @@
         <v>90</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>277</v>
+        <v>103</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>665</v>
+        <v>307</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>666</v>
+        <v>308</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="O164" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>78</v>
       </c>
@@ -21915,11 +21942,13 @@
         <v>78</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="Y164" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y164" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z164" t="s" s="2">
-        <v>668</v>
+        <v>78</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>78</v>
@@ -21937,7 +21966,7 @@
         <v>78</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>664</v>
+        <v>311</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -21955,7 +21984,7 @@
         <v>78</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>669</v>
+        <v>78</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>78</v>
@@ -21964,10 +21993,10 @@
         <v>78</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
         <v>670</v>
       </c>
@@ -21986,24 +22015,26 @@
         <v>89</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J165" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>104</v>
+        <v>671</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N165" s="2"/>
+        <v>672</v>
+      </c>
+      <c r="N165" t="s" s="2">
+        <v>673</v>
+      </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>78</v>
@@ -22028,13 +22059,11 @@
         <v>78</v>
       </c>
       <c r="X165" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y165" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Y165" s="2"/>
       <c r="Z165" t="s" s="2">
-        <v>78</v>
+        <v>674</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>78</v>
@@ -22052,7 +22081,7 @@
         <v>78</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>106</v>
+        <v>670</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -22064,13 +22093,13 @@
         <v>78</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK165" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>78</v>
+        <v>675</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>78</v>
@@ -22084,21 +22113,21 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>78</v>
@@ -22110,17 +22139,15 @@
         <v>78</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N166" s="2"/>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>78</v>
@@ -22157,31 +22184,31 @@
         <v>78</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC166" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD166" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE166" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>78</v>
@@ -22201,14 +22228,14 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
@@ -22224,23 +22251,21 @@
         <v>78</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>673</v>
+        <v>110</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>674</v>
+        <v>111</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>78</v>
       </c>
@@ -22276,19 +22301,19 @@
         <v>78</v>
       </c>
       <c r="AB167" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC167" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD167" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE167" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22300,7 +22325,7 @@
         <v>78</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>78</v>
@@ -22315,15 +22340,15 @@
         <v>78</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22334,7 +22359,7 @@
         <v>79</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>78</v>
@@ -22343,19 +22368,23 @@
         <v>78</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>104</v>
+        <v>679</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N168" s="2"/>
-      <c r="O168" s="2"/>
+        <v>680</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O168" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P168" t="s" s="2">
         <v>78</v>
       </c>
@@ -22403,19 +22432,19 @@
         <v>78</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI168" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>78</v>
@@ -22430,26 +22459,26 @@
         <v>78</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H169" t="s" s="2">
         <v>78</v>
@@ -22461,17 +22490,15 @@
         <v>78</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N169" s="2"/>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>78</v>
@@ -22508,31 +22535,31 @@
         <v>78</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK169" t="s" s="2">
         <v>78</v>
@@ -22550,48 +22577,46 @@
         <v>78</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H170" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I170" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J170" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
         <v>78</v>
       </c>
@@ -22600,7 +22625,7 @@
         <v>78</v>
       </c>
       <c r="S170" t="s" s="2">
-        <v>678</v>
+        <v>78</v>
       </c>
       <c r="T170" t="s" s="2">
         <v>78</v>
@@ -22627,31 +22652,31 @@
         <v>78</v>
       </c>
       <c r="AB170" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC170" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD170" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE170" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI170" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>78</v>
@@ -22666,15 +22691,15 @@
         <v>78</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="171" hidden="true">
+    <row r="171">
       <c r="A171" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22688,7 +22713,7 @@
         <v>89</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>78</v>
@@ -22697,18 +22722,20 @@
         <v>90</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O171" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O171" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P171" t="s" s="2">
         <v>78</v>
       </c>
@@ -22717,7 +22744,7 @@
         <v>78</v>
       </c>
       <c r="S171" t="s" s="2">
-        <v>78</v>
+        <v>684</v>
       </c>
       <c r="T171" t="s" s="2">
         <v>78</v>
@@ -22756,7 +22783,7 @@
         <v>78</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
@@ -22783,15 +22810,15 @@
         <v>78</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22805,7 +22832,7 @@
         <v>89</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>78</v>
@@ -22814,18 +22841,18 @@
         <v>90</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N172" s="2"/>
-      <c r="O172" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>78</v>
       </c>
@@ -22873,7 +22900,7 @@
         <v>78</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -22900,15 +22927,15 @@
         <v>78</v>
       </c>
       <c r="AO172" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
-    <row r="173" hidden="true">
+    <row r="173">
       <c r="A173" t="s" s="2">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22922,7 +22949,7 @@
         <v>89</v>
       </c>
       <c r="H173" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I173" t="s" s="2">
         <v>78</v>
@@ -22931,17 +22958,17 @@
         <v>90</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>78</v>
@@ -22990,7 +23017,7 @@
         <v>78</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
@@ -23017,15 +23044,15 @@
         <v>78</v>
       </c>
       <c r="AO173" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23048,19 +23075,17 @@
         <v>90</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N174" s="2"/>
       <c r="O174" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>78</v>
@@ -23109,7 +23134,7 @@
         <v>78</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>79</v>
@@ -23136,15 +23161,15 @@
         <v>78</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23167,19 +23192,19 @@
         <v>90</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>78</v>
@@ -23228,7 +23253,7 @@
         <v>78</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>79</v>
@@ -23255,15 +23280,15 @@
         <v>78</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>312</v>
+        <v>266</v>
       </c>
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23274,7 +23299,7 @@
         <v>79</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>78</v>
@@ -23283,21 +23308,23 @@
         <v>78</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>685</v>
+        <v>103</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>686</v>
+        <v>307</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>687</v>
+        <v>308</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="O176" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O176" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P176" t="s" s="2">
         <v>78</v>
       </c>
@@ -23345,13 +23372,13 @@
         <v>78</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>684</v>
+        <v>311</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>78</v>
@@ -23372,15 +23399,15 @@
         <v>78</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23394,7 +23421,7 @@
         <v>80</v>
       </c>
       <c r="H177" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I177" t="s" s="2">
         <v>78</v>
@@ -23403,16 +23430,16 @@
         <v>78</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>277</v>
+        <v>691</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -23438,29 +23465,31 @@
         <v>78</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>693</v>
+        <v>78</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>694</v>
+        <v>78</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB177" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AC177" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC177" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD177" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE177" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -23478,28 +23507,26 @@
         <v>78</v>
       </c>
       <c r="AL177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO177" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="178" hidden="true">
+      <c r="A178" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="AM177" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN177" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO177" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s" s="2">
-        <v>696</v>
-      </c>
       <c r="B178" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="C178" t="s" s="2">
-        <v>697</v>
-      </c>
+        <v>695</v>
+      </c>
+      <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
         <v>78</v>
       </c>
@@ -23523,13 +23550,13 @@
         <v>277</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23555,29 +23582,29 @@
         <v>78</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="Y178" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="Y178" t="s" s="2">
+        <v>699</v>
+      </c>
       <c r="Z178" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC178" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="AC178" s="2"/>
       <c r="AD178" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE178" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23595,7 +23622,7 @@
         <v>78</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>78</v>
+        <v>701</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>78</v>
@@ -23607,14 +23634,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="179" hidden="true">
+    <row r="179">
       <c r="A179" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="C179" s="2"/>
+        <v>695</v>
+      </c>
+      <c r="C179" t="s" s="2">
+        <v>703</v>
+      </c>
       <c r="D179" t="s" s="2">
         <v>78</v>
       </c>
@@ -23623,10 +23652,10 @@
         <v>79</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>78</v>
@@ -23635,15 +23664,17 @@
         <v>78</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>104</v>
+        <v>696</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N179" s="2"/>
+        <v>697</v>
+      </c>
+      <c r="N179" t="s" s="2">
+        <v>698</v>
+      </c>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
         <v>78</v>
@@ -23668,13 +23699,11 @@
         <v>78</v>
       </c>
       <c r="X179" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y179" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Y179" s="2"/>
       <c r="Z179" t="s" s="2">
-        <v>78</v>
+        <v>704</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>78</v>
@@ -23692,19 +23721,19 @@
         <v>78</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>106</v>
+        <v>695</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH179" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI179" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>78</v>
@@ -23724,21 +23753,21 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>78</v>
@@ -23750,17 +23779,15 @@
         <v>78</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N180" s="2"/>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>78</v>
@@ -23797,31 +23824,31 @@
         <v>78</v>
       </c>
       <c r="AB180" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC180" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD180" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE180" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK180" t="s" s="2">
         <v>78</v>
@@ -23841,14 +23868,14 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
@@ -23864,23 +23891,21 @@
         <v>78</v>
       </c>
       <c r="J181" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>705</v>
+        <v>110</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>706</v>
+        <v>111</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O181" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
         <v>78</v>
       </c>
@@ -23916,19 +23941,19 @@
         <v>78</v>
       </c>
       <c r="AB181" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC181" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD181" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE181" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>79</v>
@@ -23940,7 +23965,7 @@
         <v>78</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK181" t="s" s="2">
         <v>78</v>
@@ -23955,15 +23980,15 @@
         <v>78</v>
       </c>
       <c r="AO181" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23974,7 +23999,7 @@
         <v>79</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H182" t="s" s="2">
         <v>78</v>
@@ -23983,19 +24008,23 @@
         <v>78</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>104</v>
+        <v>711</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N182" s="2"/>
-      <c r="O182" s="2"/>
+        <v>712</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P182" t="s" s="2">
         <v>78</v>
       </c>
@@ -24043,19 +24072,19 @@
         <v>78</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH182" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI182" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK182" t="s" s="2">
         <v>78</v>
@@ -24070,26 +24099,26 @@
         <v>78</v>
       </c>
       <c r="AO182" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H183" t="s" s="2">
         <v>78</v>
@@ -24101,17 +24130,15 @@
         <v>78</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N183" s="2"/>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>78</v>
@@ -24148,31 +24175,31 @@
         <v>78</v>
       </c>
       <c r="AB183" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC183" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD183" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE183" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH183" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI183" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>78</v>
@@ -24192,21 +24219,21 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>78</v>
@@ -24215,23 +24242,21 @@
         <v>78</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O184" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
         <v>78</v>
       </c>
@@ -24240,7 +24265,7 @@
         <v>78</v>
       </c>
       <c r="S184" t="s" s="2">
-        <v>713</v>
+        <v>78</v>
       </c>
       <c r="T184" t="s" s="2">
         <v>78</v>
@@ -24267,31 +24292,31 @@
         <v>78</v>
       </c>
       <c r="AB184" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC184" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD184" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE184" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH184" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI184" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ184" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK184" t="s" s="2">
         <v>78</v>
@@ -24306,15 +24331,15 @@
         <v>78</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24337,18 +24362,20 @@
         <v>90</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O185" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O185" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P185" t="s" s="2">
         <v>78</v>
       </c>
@@ -24357,7 +24384,7 @@
         <v>78</v>
       </c>
       <c r="S185" t="s" s="2">
-        <v>78</v>
+        <v>719</v>
       </c>
       <c r="T185" t="s" s="2">
         <v>78</v>
@@ -24396,7 +24423,7 @@
         <v>78</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>79</v>
@@ -24423,15 +24450,15 @@
         <v>78</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24439,13 +24466,13 @@
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G186" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H186" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I186" t="s" s="2">
         <v>78</v>
@@ -24454,18 +24481,18 @@
         <v>90</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N186" s="2"/>
-      <c r="O186" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N186" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
         <v>78</v>
       </c>
@@ -24513,7 +24540,7 @@
         <v>78</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -24540,15 +24567,15 @@
         <v>78</v>
       </c>
       <c r="AO186" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
-    <row r="187" hidden="true">
+    <row r="187">
       <c r="A187" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24556,13 +24583,13 @@
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G187" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H187" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I187" t="s" s="2">
         <v>78</v>
@@ -24571,17 +24598,17 @@
         <v>90</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>78</v>
@@ -24630,7 +24657,7 @@
         <v>78</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -24657,15 +24684,15 @@
         <v>78</v>
       </c>
       <c r="AO187" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24688,19 +24715,17 @@
         <v>90</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N188" s="2"/>
       <c r="O188" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>78</v>
@@ -24749,7 +24774,7 @@
         <v>78</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -24776,15 +24801,15 @@
         <v>78</v>
       </c>
       <c r="AO188" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24807,19 +24832,19 @@
         <v>90</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>78</v>
@@ -24868,7 +24893,7 @@
         <v>78</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
@@ -24895,19 +24920,17 @@
         <v>78</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>312</v>
+        <v>266</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="C190" t="s" s="2">
-        <v>725</v>
-      </c>
+        <v>729</v>
+      </c>
+      <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
         <v>78</v>
       </c>
@@ -24916,30 +24939,32 @@
         <v>79</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J190" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I190" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J190" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K190" t="s" s="2">
-        <v>277</v>
+        <v>103</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>690</v>
+        <v>307</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>691</v>
+        <v>308</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="O190" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O190" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P190" t="s" s="2">
         <v>78</v>
       </c>
@@ -24963,11 +24988,13 @@
         <v>78</v>
       </c>
       <c r="X190" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="Y190" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y190" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z190" t="s" s="2">
-        <v>726</v>
+        <v>78</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>78</v>
@@ -24985,13 +25012,13 @@
         <v>78</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>689</v>
+        <v>311</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH190" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI190" t="s" s="2">
         <v>78</v>
@@ -25012,17 +25039,19 @@
         <v>78</v>
       </c>
       <c r="AO190" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
     </row>
-    <row r="191" hidden="true">
+    <row r="191">
       <c r="A191" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="C191" s="2"/>
+        <v>695</v>
+      </c>
+      <c r="C191" t="s" s="2">
+        <v>731</v>
+      </c>
       <c r="D191" t="s" s="2">
         <v>78</v>
       </c>
@@ -25031,10 +25060,10 @@
         <v>79</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H191" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I191" t="s" s="2">
         <v>78</v>
@@ -25043,15 +25072,17 @@
         <v>78</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>104</v>
+        <v>696</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N191" s="2"/>
+        <v>697</v>
+      </c>
+      <c r="N191" t="s" s="2">
+        <v>698</v>
+      </c>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
         <v>78</v>
@@ -25076,13 +25107,11 @@
         <v>78</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
-        <v>78</v>
+        <v>732</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>78</v>
@@ -25100,19 +25129,19 @@
         <v>78</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>106</v>
+        <v>695</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH191" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI191" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK191" t="s" s="2">
         <v>78</v>
@@ -25132,21 +25161,21 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E192" s="2"/>
       <c r="F192" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>78</v>
@@ -25158,17 +25187,15 @@
         <v>78</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N192" s="2"/>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
         <v>78</v>
@@ -25205,31 +25232,31 @@
         <v>78</v>
       </c>
       <c r="AB192" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC192" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD192" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE192" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI192" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK192" t="s" s="2">
         <v>78</v>
@@ -25249,14 +25276,14 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
@@ -25272,23 +25299,21 @@
         <v>78</v>
       </c>
       <c r="J193" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>730</v>
+        <v>110</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>731</v>
+        <v>111</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O193" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
         <v>78</v>
       </c>
@@ -25324,19 +25349,19 @@
         <v>78</v>
       </c>
       <c r="AB193" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC193" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD193" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE193" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>79</v>
@@ -25348,7 +25373,7 @@
         <v>78</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>78</v>
@@ -25363,15 +25388,15 @@
         <v>78</v>
       </c>
       <c r="AO193" t="s" s="2">
-        <v>288</v>
+        <v>78</v>
       </c>
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25382,7 +25407,7 @@
         <v>79</v>
       </c>
       <c r="G194" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H194" t="s" s="2">
         <v>78</v>
@@ -25391,19 +25416,23 @@
         <v>78</v>
       </c>
       <c r="J194" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>104</v>
+        <v>736</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N194" s="2"/>
-      <c r="O194" s="2"/>
+        <v>737</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="O194" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P194" t="s" s="2">
         <v>78</v>
       </c>
@@ -25451,19 +25480,19 @@
         <v>78</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>106</v>
+        <v>287</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH194" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI194" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ194" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK194" t="s" s="2">
         <v>78</v>
@@ -25478,26 +25507,26 @@
         <v>78</v>
       </c>
       <c r="AO194" t="s" s="2">
-        <v>78</v>
+        <v>288</v>
       </c>
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G195" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H195" t="s" s="2">
         <v>78</v>
@@ -25509,17 +25538,15 @@
         <v>78</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N195" s="2"/>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
         <v>78</v>
@@ -25556,31 +25583,31 @@
         <v>78</v>
       </c>
       <c r="AB195" t="s" s="2">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="AC195" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AD195" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE195" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH195" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI195" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK195" t="s" s="2">
         <v>78</v>
@@ -25600,21 +25627,21 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G196" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H196" t="s" s="2">
         <v>78</v>
@@ -25623,23 +25650,21 @@
         <v>78</v>
       </c>
       <c r="J196" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O196" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
         <v>78</v>
       </c>
@@ -25648,7 +25673,7 @@
         <v>78</v>
       </c>
       <c r="S196" t="s" s="2">
-        <v>735</v>
+        <v>78</v>
       </c>
       <c r="T196" t="s" s="2">
         <v>78</v>
@@ -25675,31 +25700,31 @@
         <v>78</v>
       </c>
       <c r="AB196" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="AC196" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AD196" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE196" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH196" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI196" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ196" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK196" t="s" s="2">
         <v>78</v>
@@ -25714,15 +25739,15 @@
         <v>78</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>236</v>
+        <v>78</v>
       </c>
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25730,7 +25755,7 @@
       </c>
       <c r="E197" s="2"/>
       <c r="F197" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G197" t="s" s="2">
         <v>89</v>
@@ -25745,18 +25770,20 @@
         <v>90</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O197" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="O197" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P197" t="s" s="2">
         <v>78</v>
       </c>
@@ -25765,7 +25792,7 @@
         <v>78</v>
       </c>
       <c r="S197" t="s" s="2">
-        <v>78</v>
+        <v>741</v>
       </c>
       <c r="T197" t="s" s="2">
         <v>78</v>
@@ -25804,7 +25831,7 @@
         <v>78</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>79</v>
@@ -25831,15 +25858,15 @@
         <v>78</v>
       </c>
       <c r="AO197" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -25847,7 +25874,7 @@
       </c>
       <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G198" t="s" s="2">
         <v>89</v>
@@ -25862,18 +25889,18 @@
         <v>90</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N198" s="2"/>
-      <c r="O198" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N198" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
         <v>78</v>
       </c>
@@ -25921,7 +25948,7 @@
         <v>78</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>79</v>
@@ -25948,15 +25975,15 @@
         <v>78</v>
       </c>
       <c r="AO198" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -25964,7 +25991,7 @@
       </c>
       <c r="E199" s="2"/>
       <c r="F199" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G199" t="s" s="2">
         <v>89</v>
@@ -25979,17 +26006,17 @@
         <v>90</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>78</v>
@@ -26038,7 +26065,7 @@
         <v>78</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>79</v>
@@ -26065,15 +26092,15 @@
         <v>78</v>
       </c>
       <c r="AO199" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26096,19 +26123,17 @@
         <v>90</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N200" s="2"/>
       <c r="O200" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>78</v>
@@ -26157,7 +26182,7 @@
         <v>78</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>79</v>
@@ -26184,15 +26209,15 @@
         <v>78</v>
       </c>
       <c r="AO200" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26215,19 +26240,19 @@
         <v>90</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>78</v>
@@ -26276,7 +26301,7 @@
         <v>78</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>79</v>
@@ -26303,15 +26328,15 @@
         <v>78</v>
       </c>
       <c r="AO201" t="s" s="2">
-        <v>312</v>
+        <v>266</v>
       </c>
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>741</v>
+        <v>729</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26322,7 +26347,7 @@
         <v>79</v>
       </c>
       <c r="G202" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H202" t="s" s="2">
         <v>78</v>
@@ -26331,20 +26356,22 @@
         <v>78</v>
       </c>
       <c r="J202" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>742</v>
+        <v>103</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>743</v>
+        <v>307</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="N202" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N202" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O202" t="s" s="2">
-        <v>745</v>
+        <v>310</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>78</v>
@@ -26393,13 +26420,13 @@
         <v>78</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>741</v>
+        <v>311</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH202" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI202" t="s" s="2">
         <v>78</v>
@@ -26420,15 +26447,15 @@
         <v>78</v>
       </c>
       <c r="AO202" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -26451,16 +26478,18 @@
         <v>78</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>277</v>
+        <v>748</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="N203" s="2"/>
-      <c r="O203" s="2"/>
+      <c r="O203" t="s" s="2">
+        <v>751</v>
+      </c>
       <c r="P203" t="s" s="2">
         <v>78</v>
       </c>
@@ -26484,13 +26513,13 @@
         <v>78</v>
       </c>
       <c r="X203" t="s" s="2">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="Y203" t="s" s="2">
-        <v>749</v>
+        <v>78</v>
       </c>
       <c r="Z203" t="s" s="2">
-        <v>750</v>
+        <v>78</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>78</v>
@@ -26508,7 +26537,7 @@
         <v>78</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>79</v>
@@ -26538,12 +26567,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -26557,7 +26586,7 @@
         <v>80</v>
       </c>
       <c r="H204" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I204" t="s" s="2">
         <v>78</v>
@@ -26566,7 +26595,7 @@
         <v>78</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>752</v>
+        <v>277</v>
       </c>
       <c r="L204" t="s" s="2">
         <v>753</v>
@@ -26599,13 +26628,13 @@
         <v>78</v>
       </c>
       <c r="X204" t="s" s="2">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="Y204" t="s" s="2">
-        <v>78</v>
+        <v>755</v>
       </c>
       <c r="Z204" t="s" s="2">
-        <v>78</v>
+        <v>756</v>
       </c>
       <c r="AA204" t="s" s="2">
         <v>78</v>
@@ -26623,7 +26652,7 @@
         <v>78</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>79</v>
@@ -26644,16 +26673,16 @@
         <v>78</v>
       </c>
       <c r="AM204" t="s" s="2">
-        <v>755</v>
+        <v>78</v>
       </c>
       <c r="AN204" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO204" t="s" s="2">
-        <v>756</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="205" hidden="true">
+    <row r="205">
       <c r="A205" t="s" s="2">
         <v>757</v>
       </c>
@@ -26672,7 +26701,7 @@
         <v>80</v>
       </c>
       <c r="H205" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I205" t="s" s="2">
         <v>78</v>
@@ -26681,13 +26710,13 @@
         <v>78</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>584</v>
+        <v>758</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
@@ -26759,21 +26788,21 @@
         <v>78</v>
       </c>
       <c r="AM205" t="s" s="2">
-        <v>78</v>
+        <v>761</v>
       </c>
       <c r="AN205" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO205" t="s" s="2">
-        <v>78</v>
+        <v>762</v>
       </c>
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -26784,7 +26813,7 @@
         <v>79</v>
       </c>
       <c r="G206" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H206" t="s" s="2">
         <v>78</v>
@@ -26796,13 +26825,13 @@
         <v>78</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>103</v>
+        <v>585</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>104</v>
+        <v>764</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>105</v>
+        <v>765</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -26853,19 +26882,19 @@
         <v>78</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>106</v>
+        <v>763</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH206" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI206" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK206" t="s" s="2">
         <v>78</v>
@@ -26885,21 +26914,21 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E207" s="2"/>
       <c r="F207" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G207" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H207" t="s" s="2">
         <v>78</v>
@@ -26911,17 +26940,15 @@
         <v>78</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N207" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N207" s="2"/>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
         <v>78</v>
@@ -26970,19 +26997,19 @@
         <v>78</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH207" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI207" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AK207" t="s" s="2">
         <v>78</v>
@@ -27002,14 +27029,14 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
-        <v>591</v>
+        <v>108</v>
       </c>
       <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
@@ -27022,26 +27049,24 @@
         <v>78</v>
       </c>
       <c r="I208" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J208" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K208" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>592</v>
+        <v>110</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>593</v>
+        <v>111</v>
       </c>
       <c r="N208" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="O208" t="s" s="2">
-        <v>340</v>
-      </c>
+      <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
         <v>78</v>
       </c>
@@ -27089,7 +27114,7 @@
         <v>78</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>594</v>
+        <v>116</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>79</v>
@@ -27121,42 +27146,46 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
-        <v>78</v>
+        <v>592</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I209" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>277</v>
+        <v>109</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>764</v>
+        <v>593</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="N209" s="2"/>
-      <c r="O209" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="N209" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O209" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P209" t="s" s="2">
         <v>78</v>
       </c>
@@ -27180,13 +27209,13 @@
         <v>78</v>
       </c>
       <c r="X209" t="s" s="2">
-        <v>168</v>
+        <v>78</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>766</v>
+        <v>78</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>767</v>
+        <v>78</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>78</v>
@@ -27204,19 +27233,19 @@
         <v>78</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>763</v>
+        <v>595</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH209" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI209" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="AK209" t="s" s="2">
         <v>78</v>
@@ -27236,10 +27265,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27247,7 +27276,7 @@
       </c>
       <c r="E210" s="2"/>
       <c r="F210" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G210" t="s" s="2">
         <v>89</v>
@@ -27262,7 +27291,7 @@
         <v>78</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>769</v>
+        <v>277</v>
       </c>
       <c r="L210" t="s" s="2">
         <v>770</v>
@@ -27295,13 +27324,13 @@
         <v>78</v>
       </c>
       <c r="X210" t="s" s="2">
-        <v>78</v>
+        <v>168</v>
       </c>
       <c r="Y210" t="s" s="2">
-        <v>78</v>
+        <v>772</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>78</v>
+        <v>773</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>78</v>
@@ -27319,10 +27348,10 @@
         <v>78</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AG210" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH210" t="s" s="2">
         <v>89</v>
@@ -27351,10 +27380,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -27362,10 +27391,10 @@
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>78</v>
@@ -27377,20 +27406,16 @@
         <v>78</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="N211" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="O211" t="s" s="2">
         <v>777</v>
       </c>
+      <c r="N211" s="2"/>
+      <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
         <v>78</v>
       </c>
@@ -27438,13 +27463,13 @@
         <v>78</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="AG211" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI211" t="s" s="2">
         <v>78</v>
@@ -27496,18 +27521,20 @@
         <v>78</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>277</v>
+        <v>779</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="O212" s="2"/>
+        <v>782</v>
+      </c>
+      <c r="O212" t="s" s="2">
+        <v>783</v>
+      </c>
       <c r="P212" t="s" s="2">
         <v>78</v>
       </c>
@@ -27531,13 +27558,13 @@
         <v>78</v>
       </c>
       <c r="X212" t="s" s="2">
-        <v>154</v>
+        <v>78</v>
       </c>
       <c r="Y212" t="s" s="2">
-        <v>781</v>
+        <v>78</v>
       </c>
       <c r="Z212" t="s" s="2">
-        <v>782</v>
+        <v>78</v>
       </c>
       <c r="AA212" t="s" s="2">
         <v>78</v>
@@ -27585,8 +27612,125 @@
         <v>78</v>
       </c>
     </row>
+    <row r="213" hidden="true">
+      <c r="A213" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="B213" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="C213" s="2"/>
+      <c r="D213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E213" s="2"/>
+      <c r="F213" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G213" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K213" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L213" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="M213" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="N213" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="O213" s="2"/>
+      <c r="P213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q213" s="2"/>
+      <c r="R213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X213" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="Y213" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="Z213" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="AA213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF213" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="AG213" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH213" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ213" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN213" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO213" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AO212">
+  <autoFilter ref="A1:AO213">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -27596,7 +27740,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI211">
+  <conditionalFormatting sqref="A2:AI212">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-melanom-exzision.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
